--- a/Result/05-01-25/NASDAQstock_05-01-25period252RS90.xlsx
+++ b/Result/05-01-25/NASDAQstock_05-01-25period252RS90.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/01-05-25/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding Project/StockAnalysis/Result/05-01-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF8EF59-2E0C-5942-B345-1F56D2D47E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00AF4A5-643B-FA46-B0BE-E9D0FE2B0E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
